--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
-  <autoFilter ref="A1:CO12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO22" headerRowCount="1">
+  <autoFilter ref="A1:CO22"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$22)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$22)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CO22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2953,22 +2953,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>851644f016cd4f3d</t>
+          <t>d214d4e301eb402a</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3003,26 +3003,26 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.607321</v>
+        <v>0.736846</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.227093</v>
+        <v>0.06687899999999999</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
@@ -3031,21 +3031,35 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:28:05.785838Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3055,7 +3069,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3086,32 +3100,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3164,7 +3178,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:11.610199Z</t>
+          <t>2026-07-27T10:27:02.394501Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3174,13 +3188,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3214,12 +3228,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>13eb741cf39f44b6</t>
+          <t>43fbd7ae8a454468</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3229,7 +3243,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>63352</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3239,12 +3253,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3264,23 +3278,23 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.736846</v>
+        <v>0.862507</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.107216</v>
+        <v>0.253132</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>2</v>
@@ -3292,21 +3306,35 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:28:06.987937Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-exruby-erx-2026-07-27).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3347,32 +3375,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3425,7 +3453,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:12.664245Z</t>
+          <t>2026-07-27T10:27:03.352513Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3435,13 +3463,13 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
@@ -3475,22 +3503,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>577cc1bfbaf04804</t>
+          <t>4525ee5e7e904c7a</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:30:00Z</t>
+          <t>2026-07-27T12:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>60736</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3500,12 +3528,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3525,26 +3553,26 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-194</v>
+        <v>150</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.5</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.4</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.735192</v>
+        <v>0.610293</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.07532800000000001</v>
+        <v>0.210293</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
@@ -3553,21 +3581,35 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:28:08.136051Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-nvo-atp-2026-07-27).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3577,7 +3619,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3608,32 +3650,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3686,7 +3728,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:17.438646Z</t>
+          <t>2026-07-27T10:27:05.476395Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3696,13 +3738,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-194</v>
+        <v>150</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.5</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.4</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3736,22 +3778,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>a5db31543d9941f6</t>
+          <t>269bbdff6793467f</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T13:31:52.156513Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:00Z</t>
+          <t>2026-07-27T14:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3761,12 +3803,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3786,23 +3828,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.659512</v>
+        <v>0.652309</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.050137</v>
+        <v>0.032537</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>2</v>
@@ -3814,21 +3856,35 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:32:27.416588Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-ica-2026-07-27).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3838,7 +3894,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3869,32 +3925,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3912,7 +3968,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3927,7 +3983,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3947,7 +4003,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:17.953712Z</t>
+          <t>2026-07-27T13:31:26.771058Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3957,13 +4013,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -3997,22 +4053,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>a0beb7bad3134fda</t>
+          <t>535821dca49e400c</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T13:31:52.156513Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:00:00Z</t>
+          <t>2026-07-27T16:30:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4022,12 +4078,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4047,23 +4103,23 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.70196</v>
+        <v>0.658722</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.082188</v>
+        <v>0.049347</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>2</v>
@@ -4075,21 +4131,35 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:32.390954Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4130,32 +4200,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4173,7 +4243,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4188,7 +4258,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4208,7 +4278,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:18.459256Z</t>
+          <t>2026-07-27T13:31:31.182868Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4218,13 +4288,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4258,12 +4328,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>c3d7c5b84e5f45ae</t>
+          <t>59095b1c59d34be6</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T16:36:41.723874Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4273,7 +4343,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4283,12 +4353,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4298,7 +4368,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4308,26 +4378,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>178</v>
+        <v>-156</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2.78</v>
+        <v>1.641026</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.609375</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.573171</v>
+        <v>0.680315</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.213459</v>
+        <v>0.07094</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4336,21 +4406,35 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:33.512127Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4360,7 +4444,7 @@
       </c>
       <c r="AG12" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH12" s="24" t="n"/>
@@ -4391,32 +4475,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4434,7 +4518,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4449,7 +4533,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4469,7 +4553,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:18.919041Z</t>
+          <t>2026-07-27T16:36:23.363578Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4479,13 +4563,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>178</v>
+        <v>-156</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>2.78</v>
+        <v>1.641026</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.609375</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4516,6 +4600,2644 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>26ac854df3564725</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:41.723874Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>60794</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.506515</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.156865</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>98</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:04.146089Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:24.863764Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>b009442629df4cc1</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:10.535886Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:15:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>63492</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.65286</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.10331</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>1.6393</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:05.272028Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-aimc-mel-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>867870f5311168845ab98ba889eb7970c88200d6dbd0532dbd8a6a3de3837c1a</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>867870f5311168845ab98ba889eb7970c88200d6dbd0532dbd8a6a3de3837c1a</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:37:55.611264Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>7681c20815f547e4</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>63306</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.710969</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-enjoy-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:39.784703Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>6a4e6e1f199546c9</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>64432</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.509533</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.159883</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:40.889369Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>8b7742d48b154a4c</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>63359</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.589686</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.070455</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:42.419976Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>f01f527cad484709</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>64367</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.525641</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.06481199999999999</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:42.912018Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>a1ff007a7d104399</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>63360</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.53791</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.057141</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:45.363088Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>147b001ceaa24335</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>63362</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.548241</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.107712</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-sparta-g2a-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:47.940507Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>2b723c7fba9643ee</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>63363</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.553566</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.084082</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-cshp-lav-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:49.411771Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>98542e97ce3841ee</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:08:42.519814Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>63706</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.609287</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.029455</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:08:19.728443Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO22" headerRowCount="1">
-  <autoFilter ref="A1:CO22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO21" headerRowCount="1">
+  <autoFilter ref="A1:CO21"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$22)</f>
+        <f>COUNTA('Picks'!$A$2:$A$21)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$22)</f>
+        <f>SUM('Picks'!$BY$2:$BY$21)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO22"/>
+  <dimension ref="A1:CO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5153,12 +5153,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>7681c20815f547e4</t>
+          <t>b130a7489baa41ec</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T05:05:50.168792Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5231,18 +5231,32 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:40.671751Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-enjoy-2026-07-28).</t>
@@ -5255,7 +5269,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5329,7 +5343,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5344,7 +5358,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5364,7 +5378,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:39.784703Z</t>
+          <t>2026-07-28T05:05:25.710714Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5414,22 +5428,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>6a4e6e1f199546c9</t>
+          <t>b3a9bdbbf6b748de</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T05:05:50.168792Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T10:00:00Z</t>
+          <t>2026-07-28T08:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>64432</t>
+          <t>63706</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5439,12 +5453,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5464,26 +5478,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>186</v>
+        <v>-144</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2.86</v>
+        <v>1.694444</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.590164</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.509533</v>
+        <v>0.609287</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.159883</v>
+        <v>0.019123</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5492,21 +5506,35 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:41.886189Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5547,32 +5575,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5590,7 +5618,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5605,7 +5633,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5625,7 +5653,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:40.889369Z</t>
+          <t>2026-07-28T05:05:26.235601Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5635,13 +5663,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>186</v>
+        <v>-144</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>2.86</v>
+        <v>1.694444</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.590164</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5675,22 +5703,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>8b7742d48b154a4c</t>
+          <t>d680f0c63c144b2a</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:00:00Z</t>
+          <t>2026-07-28T10:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>63359</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5700,12 +5728,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5715,7 +5743,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -5725,26 +5753,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-108</v>
+        <v>150</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.5</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.4</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.589686</v>
+        <v>0.509533</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.070455</v>
+        <v>0.109533</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5753,21 +5781,35 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:45.452613Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5777,7 +5819,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -5808,32 +5850,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5851,7 +5893,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5866,7 +5908,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5886,7 +5928,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:42.419976Z</t>
+          <t>2026-07-28T08:11:31.472875Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5896,13 +5938,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-108</v>
+        <v>150</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.5</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.4</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5936,12 +5978,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>f01f527cad484709</t>
+          <t>1230e8ccb3f14468</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -5951,7 +5993,7 @@
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>63359</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -5961,12 +6003,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -5986,26 +6028,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.525641</v>
+        <v>0.589686</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.06481199999999999</v>
+        <v>0.089686</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6014,21 +6056,35 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:46.743433Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6038,7 +6094,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6069,32 +6125,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6112,7 +6168,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6127,7 +6183,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6147,7 +6203,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:42.912018Z</t>
+          <t>2026-07-28T08:11:32.486834Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6157,13 +6213,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6197,22 +6253,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>a1ff007a7d104399</t>
+          <t>f939627a80c7422c</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:00:00Z</t>
+          <t>2026-07-28T11:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>63360</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6222,12 +6278,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6247,49 +6303,63 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.469484</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.53791</v>
+        <v>0.525641</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.057141</v>
+        <v>0.056157</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S19" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T19" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:47.865907Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6330,32 +6400,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6373,7 +6443,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6388,7 +6458,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6408,7 +6478,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:45.363088Z</t>
+          <t>2026-07-28T08:11:33.028196Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6418,13 +6488,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.469484</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6458,22 +6528,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>147b001ceaa24335</t>
+          <t>0961e2f1cea44460</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T11:17:59.302295Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:00:00Z</t>
+          <t>2026-07-28T14:00:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>63362</t>
+          <t>63360</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6483,12 +6553,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6508,23 +6578,23 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.469484</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.548241</v>
+        <v>0.53772</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.107712</v>
+        <v>0.068236</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>1</v>
@@ -6550,7 +6620,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-sparta-g2a-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6591,32 +6661,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6634,7 +6704,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6649,7 +6719,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6669,7 +6739,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:47.940507Z</t>
+          <t>2026-07-28T11:17:40.063714Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6679,13 +6749,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.469484</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6719,22 +6789,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>2b723c7fba9643ee</t>
+          <t>3ade7d7fea21469e</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T14:24:09.023643Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:00:00Z</t>
+          <t>2026-07-28T15:00:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6744,12 +6814,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6759,7 +6829,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -6769,26 +6839,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.553566</v>
+        <v>0.907919</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.084082</v>
+        <v>0.248055</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -6811,7 +6881,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-cshp-lav-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-tdk-baks-2026-07-28).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -6852,32 +6922,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -6895,7 +6965,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>b7be26981f98c7c049773609859384b830ed2600e5d283ac2efb1545695d5e3e</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -6910,7 +6980,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>b7be26981f98c7c049773609859384b830ed2600e5d283ac2efb1545695d5e3e</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -6930,7 +7000,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:49.411771Z</t>
+          <t>2026-07-28T14:23:49.113149Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -6940,13 +7010,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -6977,267 +7047,6 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>98542e97ce3841ee</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:08:42.519814Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>63706</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.609287</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>0.029455</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:08:19.728443Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO60" headerRowCount="1">
-  <autoFilter ref="A1:CO60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO59" headerRowCount="1">
+  <autoFilter ref="A1:CO59"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$60)</f>
+        <f>COUNTA('Picks'!$A$2:$A$59)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$60,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$59,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$60,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$59,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")+COUNTIFS('Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")+COUNTIFS('Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$60,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$59,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")/(COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")+COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")/(COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")+COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$60)/SUM('Picks'!$BX$2:$BX$60),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$59)/SUM('Picks'!$BX$2:$BX$59),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$60)</f>
+        <f>SUM('Picks'!$BY$2:$BY$59)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$60,"&lt;&gt;",'Picks'!$AB$2:$AB$60),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$59,"&lt;&gt;",'Picks'!$AB$2:$AB$59),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$60,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$60,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$59,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$59,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$60,'Picks'!$AM$2:$AM$60,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$59,'Picks'!$AM$2:$AM$59,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO60"/>
+  <dimension ref="A1:CO59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13742,18 +13742,32 @@
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+      <c r="AC46" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:59.479570Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-gs-mel-2026-07-30).</t>
@@ -13766,7 +13780,7 @@
       </c>
       <c r="AG46" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH46" s="24" t="n"/>
@@ -14264,18 +14278,32 @@
       </c>
       <c r="U48" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
+      <c r="AC48" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD48" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:23:02.123784Z</t>
+        </is>
+      </c>
       <c r="AE48" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-sinqu-bjng-2026-07-30).</t>
@@ -14288,7 +14316,7 @@
       </c>
       <c r="AG48" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH48" s="24" t="n"/>
@@ -14708,12 +14736,12 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>6313bac659bd443c</t>
+          <t>02449d5e150045ad</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -14758,23 +14786,23 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.6620780000000001</v>
+        <v>0.662039</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.171882</v>
+        <v>0.142808</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>2</v>
@@ -14800,7 +14828,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sng-frt-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-sng-frt-2026-07-30).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -14884,7 +14912,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -14899,7 +14927,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -14919,7 +14947,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:27.303905Z</t>
+          <t>2026-07-30T17:21:38.234981Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -14929,13 +14957,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -14969,12 +14997,12 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>57c914df76bf467a</t>
+          <t>a6fa3e5733c7458d</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -14984,7 +15012,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -14994,12 +15022,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15009,7 +15037,7 @@
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J51" s="25" t="n"/>
@@ -15019,26 +15047,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>138</v>
+        <v>-117</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>2.38</v>
+        <v>1.854701</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.539171</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.541443</v>
+        <v>0.576671</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>0.121275</v>
+        <v>0.0375</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15061,7 +15089,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15102,32 +15130,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15145,7 +15173,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15160,7 +15188,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15180,7 +15208,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:29.676246Z</t>
+          <t>2026-07-30T17:21:40.939739Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15190,13 +15218,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>138</v>
+        <v>-117</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>2.38</v>
+        <v>1.854701</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.539171</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15230,12 +15258,12 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>baee0b7e3d1641ca</t>
+          <t>fb2b6820f3f342cc</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -15245,7 +15273,7 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>66617</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15255,12 +15283,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -15270,7 +15298,7 @@
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J52" s="25" t="n"/>
@@ -15280,23 +15308,23 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.5</v>
+        <v>0.429185</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.554756</v>
+        <v>0.541314</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>0.054756</v>
+        <v>0.112129</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="S52" s="29" t="n">
         <v>1</v>
@@ -15322,7 +15350,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15363,32 +15391,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15406,7 +15434,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15421,7 +15449,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15441,7 +15469,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:30.122924Z</t>
+          <t>2026-07-30T17:21:41.486408Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15451,13 +15479,13 @@
       </c>
       <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.5</v>
+        <v>0.429185</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
@@ -15491,12 +15519,12 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>702e577c228c4a68</t>
+          <t>695c57972aeb4e55</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -15506,7 +15534,7 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>66617</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -15516,12 +15544,12 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
@@ -15541,26 +15569,26 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.576464</v>
+        <v>0.5549500000000001</v>
       </c>
       <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.037293</v>
+        <v>0.045146</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
@@ -15583,7 +15611,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -15624,32 +15652,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -15667,7 +15695,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -15682,7 +15710,7 @@
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -15702,7 +15730,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:31.539734Z</t>
+          <t>2026-07-30T17:21:42.057537Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -15712,13 +15740,13 @@
       </c>
       <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -15752,12 +15780,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>f232d84e65d644df</t>
+          <t>f3cc735549854f44</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -15811,11 +15839,11 @@
         <v>0.480769</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.5433210000000001</v>
+        <v>0.543193</v>
       </c>
       <c r="P54" s="28" t="n"/>
       <c r="Q54" s="28" t="n">
-        <v>0.062552</v>
+        <v>0.062424</v>
       </c>
       <c r="R54" s="26" t="n">
         <v>51</v>
@@ -15928,7 +15956,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -15943,7 +15971,7 @@
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -15963,7 +15991,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:33.548064Z</t>
+          <t>2026-07-30T17:21:45.323638Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -16013,12 +16041,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>f785eb0c87954b45</t>
+          <t>9061aec8fb7b422a</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16072,14 +16100,14 @@
         <v>0.519231</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.676216</v>
+        <v>0.676465</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.156985</v>
+        <v>0.157234</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S55" s="29" t="n">
         <v>2</v>
@@ -16189,7 +16217,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -16204,7 +16232,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -16224,7 +16252,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:34.094425Z</t>
+          <t>2026-07-30T17:21:45.909267Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16274,12 +16302,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>06ee58e2c05b448c</t>
+          <t>a03df21bb3684a07</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -16333,11 +16361,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.688034</v>
+        <v>0.688286</v>
       </c>
       <c r="P56" s="28" t="n"/>
       <c r="Q56" s="28" t="n">
-        <v>0.128563</v>
+        <v>0.128815</v>
       </c>
       <c r="R56" s="26" t="n">
         <v>84</v>
@@ -16450,7 +16478,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -16465,7 +16493,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -16485,7 +16513,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:34.584817Z</t>
+          <t>2026-07-30T17:21:47.628354Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16535,12 +16563,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>cbf02261a71f4419</t>
+          <t>8f0e5f68168e4055</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -16594,11 +16622,11 @@
         <v>0.480769</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.71909</v>
+        <v>0.719348</v>
       </c>
       <c r="P57" s="28" t="n"/>
       <c r="Q57" s="28" t="n">
-        <v>0.238321</v>
+        <v>0.238579</v>
       </c>
       <c r="R57" s="26" t="n">
         <v>100</v>
@@ -16711,7 +16739,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -16726,7 +16754,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -16746,7 +16774,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:36.505125Z</t>
+          <t>2026-07-30T17:21:49.268706Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -16796,22 +16824,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>f120ec943118405e</t>
+          <t>07cc2f64665a4723</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T12:30:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>66411</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -16821,12 +16849,12 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
@@ -16836,7 +16864,7 @@
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J58" s="25" t="n"/>
@@ -16846,23 +16874,23 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>144</v>
+        <v>-170</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2.44</v>
+        <v>1.588235</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.62963</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.671111</v>
+        <v>0.698051</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>0.261275</v>
+        <v>0.068421</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>2</v>
@@ -16888,7 +16916,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-3dmax-mouz-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -16929,32 +16957,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -16972,7 +17000,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -16987,7 +17015,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17007,7 +17035,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:39.517006Z</t>
+          <t>2026-07-30T17:21:54.000232Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17017,13 +17045,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>144</v>
+        <v>-170</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2.44</v>
+        <v>1.588235</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.62963</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17057,22 +17085,22 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>85d16ead0fa9413d</t>
+          <t>f23230eab8844796</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-07-31T17:00:00Z</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17082,12 +17110,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17107,23 +17135,23 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-170</v>
+        <v>-213</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.469484</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.680511</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.697797</v>
+        <v>0.71083</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>0.06816700000000001</v>
+        <v>0.030319</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>2</v>
@@ -17149,7 +17177,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -17190,32 +17218,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -17233,7 +17261,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -17248,7 +17276,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -17268,7 +17296,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:39.995435Z</t>
+          <t>2026-07-30T17:21:54.989141Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17278,13 +17306,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-170</v>
+        <v>-213</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.469484</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.680511</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -17315,267 +17343,6 @@
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
     </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>50c1673b8ca74c2f</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>66536</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F60" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>JiJieHao</t>
-        </is>
-      </c>
-      <c r="H60" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I60" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J60" s="25" t="n"/>
-      <c r="K60" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L60" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M60" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N60" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O60" s="28" t="n">
-        <v>0.691882</v>
-      </c>
-      <c r="P60" s="28" t="n"/>
-      <c r="Q60" s="28" t="n">
-        <v>0.011371</v>
-      </c>
-      <c r="R60" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S60" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U60" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V60" s="24" t="n"/>
-      <c r="W60" s="26" t="n"/>
-      <c r="X60" s="26" t="n"/>
-      <c r="Y60" s="25" t="n"/>
-      <c r="Z60" s="26" t="n"/>
-      <c r="AA60" s="28" t="n"/>
-      <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
-      <c r="AD60" s="24" t="n"/>
-      <c r="AE60" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF60" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG60" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH60" s="24" t="n"/>
-      <c r="AI60" s="31" t="n"/>
-      <c r="AJ60" s="31" t="n"/>
-      <c r="AK60" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL60" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM60" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN60" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO60" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP60" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AQ60" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AR60" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AS60" s="24" t="inlineStr">
-        <is>
-          <t>JiJieHao</t>
-        </is>
-      </c>
-      <c r="AT60" s="24" t="inlineStr">
-        <is>
-          <t>JiJieHao</t>
-        </is>
-      </c>
-      <c r="AU60" s="24" t="inlineStr">
-        <is>
-          <t>JiJieHao</t>
-        </is>
-      </c>
-      <c r="AV60" s="24" t="n"/>
-      <c r="AW60" s="24" t="n"/>
-      <c r="AX60" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY60" s="24" t="n"/>
-      <c r="AZ60" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA60" s="24" t="inlineStr">
-        <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
-        </is>
-      </c>
-      <c r="BB60" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC60" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD60" s="24" t="inlineStr">
-        <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
-        </is>
-      </c>
-      <c r="BE60" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF60" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG60" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:55:41.909156Z</t>
-        </is>
-      </c>
-      <c r="BI60" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ60" s="25" t="n"/>
-      <c r="BK60" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL60" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM60" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN60" s="28" t="n"/>
-      <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
-      <c r="BR60" s="28" t="n"/>
-      <c r="BS60" s="28" t="n"/>
-      <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="25" t="n"/>
-      <c r="BV60" s="29" t="n"/>
-      <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="30" t="n"/>
-      <c r="BY60" s="27" t="n"/>
-      <c r="BZ60" s="24" t="n"/>
-      <c r="CA60" s="31" t="n"/>
-      <c r="CB60" s="24" t="n"/>
-      <c r="CC60" s="24" t="n"/>
-      <c r="CD60" s="24" t="n"/>
-      <c r="CE60" s="24" t="n"/>
-      <c r="CF60" s="24" t="n"/>
-      <c r="CG60" s="24" t="n"/>
-      <c r="CH60" s="24" t="n"/>
-      <c r="CI60" s="24" t="n"/>
-      <c r="CJ60" s="24" t="n"/>
-      <c r="CK60" s="24" t="n"/>
-      <c r="CL60" s="24" t="n"/>
-      <c r="CM60" s="24" t="n"/>
-      <c r="CN60" s="24" t="n"/>
-      <c r="CO60" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO59" headerRowCount="1">
-  <autoFilter ref="A1:CO59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO60" headerRowCount="1">
+  <autoFilter ref="A1:CO60"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$59)</f>
+        <f>COUNTA('Picks'!$A$2:$A$60)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$59,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$60,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$59,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$60,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")+COUNTIFS('Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")+COUNTIFS('Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$59,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$60,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")/(COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"win")+COUNTIFS('Picks'!$BX$2:$BX$59,"&gt;0",'Picks'!$V$2:$V$59,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")/(COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"win")+COUNTIFS('Picks'!$BX$2:$BX$60,"&gt;0",'Picks'!$V$2:$V$60,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$59)/SUM('Picks'!$BX$2:$BX$59),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$60)/SUM('Picks'!$BX$2:$BX$60),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$59)</f>
+        <f>SUM('Picks'!$BY$2:$BY$60)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$59,"&lt;&gt;",'Picks'!$AB$2:$AB$59),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$60,"&lt;&gt;",'Picks'!$AB$2:$AB$60),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$59,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$59,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$60,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$60,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$59,'Picks'!$AM$2:$AM$59,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$60,'Picks'!$AM$2:$AM$60,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A14,'Picks'!$U$2:$U$59,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A14,'Picks'!$U$2:$U$60,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A15,'Picks'!$U$2:$U$59,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A15,'Picks'!$U$2:$U$60,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled",'Picks'!$V$2:$V$59,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled",'Picks'!$V$2:$V$60,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$59,'Picks'!$H$2:$H$59,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$60,'Picks'!$H$2:$H$60,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$59,'Picks'!$H$2:$H$59,$A16,'Picks'!$U$2:$U$59,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$60,'Picks'!$H$2:$H$60,$A16,'Picks'!$U$2:$U$60,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO59"/>
+  <dimension ref="A1:CO60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14997,12 +14997,12 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>a6fa3e5733c7458d</t>
+          <t>7fbc266c6b2a48bb</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:40.939739Z</t>
+          <t>2026-07-30T17:39:19.238371Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15258,12 +15258,12 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>fb2b6820f3f342cc</t>
+          <t>0813b2570a284423</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:41.486408Z</t>
+          <t>2026-07-30T17:39:19.828746Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15519,12 +15519,12 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>695c57972aeb4e55</t>
+          <t>e003296f83494e29</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -15569,26 +15569,26 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.884956</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.530516</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.5549500000000001</v>
+        <v>0.6041840000000001</v>
       </c>
       <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.045146</v>
+        <v>0.073668</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:42.057537Z</t>
+          <t>2026-07-30T17:39:20.974476Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -15740,13 +15740,13 @@
       </c>
       <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.884956</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.530516</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -15780,12 +15780,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>f3cc735549854f44</t>
+          <t>2c8b5e84b6b040e7</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:45.323638Z</t>
+          <t>2026-07-30T17:39:22.557396Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -16041,12 +16041,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>9061aec8fb7b422a</t>
+          <t>0860ffba50fa4039</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>66545</t>
+          <t>66535</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -16066,12 +16066,12 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr">
@@ -16091,23 +16091,23 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.787402</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.676465</v>
+        <v>0.688286</v>
       </c>
       <c r="P55" s="28" t="n"/>
       <c r="Q55" s="28" t="n">
-        <v>0.157234</v>
+        <v>0.128815</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="S55" s="29" t="n">
         <v>2</v>
@@ -16133,7 +16133,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-bmb-lc-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-inf-sparta-2026-07-31).</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -16174,32 +16174,32 @@
       </c>
       <c r="AP55" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AQ55" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AR55" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AS55" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AT55" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AU55" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AV55" s="24" t="n"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:45.909267Z</t>
+          <t>2026-07-30T17:39:24.025060Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16262,13 +16262,13 @@
       </c>
       <c r="BJ55" s="25" t="n"/>
       <c r="BK55" s="26" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.787402</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
@@ -16302,12 +16302,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>a03df21bb3684a07</t>
+          <t>30a2d69eab694d4b</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>66535</t>
+          <t>66545</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -16327,12 +16327,12 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
@@ -16352,23 +16352,23 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.688286</v>
+        <v>0.676465</v>
       </c>
       <c r="P56" s="28" t="n"/>
       <c r="Q56" s="28" t="n">
-        <v>0.128815</v>
+        <v>0.157234</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="S56" s="29" t="n">
         <v>2</v>
@@ -16394,7 +16394,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-inf-sparta-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-bmb-lc-2026-07-31).</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -16435,32 +16435,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:47.628354Z</t>
+          <t>2026-07-30T17:39:24.587765Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16523,13 +16523,13 @@
       </c>
       <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="BN56" s="28" t="n"/>
       <c r="BO56" s="28" t="n"/>
@@ -16563,12 +16563,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>8f0e5f68168e4055</t>
+          <t>4680846136fe4ab7</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:49.268706Z</t>
+          <t>2026-07-30T17:39:26.656791Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -16824,22 +16824,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>07cc2f64665a4723</t>
+          <t>8dcf78ecf0fc4e70</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-07-31T12:30:00Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -16849,12 +16849,12 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J58" s="25" t="n"/>
@@ -16874,23 +16874,23 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.698051</v>
+        <v>0.671079</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>0.068421</v>
+        <v>0.061704</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>2</v>
@@ -16916,7 +16916,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-3dmax-mouz-2026-07-31).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -16957,32 +16957,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:54.000232Z</t>
+          <t>2026-07-30T17:39:29.166587Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17045,13 +17045,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17085,22 +17085,22 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>f23230eab8844796</t>
+          <t>55365e77b0a24695</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T17:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>66536</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17110,12 +17110,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17135,23 +17135,23 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.71083</v>
+        <v>0.698051</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>0.030319</v>
+        <v>0.057763</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>2</v>
@@ -17177,7 +17177,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -17218,32 +17218,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -17261,7 +17261,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:54.989141Z</t>
+          <t>2026-07-30T17:39:30.737863Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17306,13 +17306,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -17343,6 +17343,267 @@
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
     </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>97137bcc49204c00</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:39:33.709014Z</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>66536</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>JiJieHao</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M60" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N60" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O60" s="28" t="n">
+        <v>0.71083</v>
+      </c>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="28" t="n">
+        <v>0.030319</v>
+      </c>
+      <c r="R60" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S60" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U60" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="n"/>
+      <c r="W60" s="26" t="n"/>
+      <c r="X60" s="26" t="n"/>
+      <c r="Y60" s="25" t="n"/>
+      <c r="Z60" s="26" t="n"/>
+      <c r="AA60" s="28" t="n"/>
+      <c r="AB60" s="28" t="n"/>
+      <c r="AC60" s="30" t="n"/>
+      <c r="AD60" s="24" t="n"/>
+      <c r="AE60" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF60" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG60" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH60" s="24" t="n"/>
+      <c r="AI60" s="31" t="n"/>
+      <c r="AJ60" s="31" t="n"/>
+      <c r="AK60" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL60" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN60" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP60" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AQ60" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AR60" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AS60" s="24" t="inlineStr">
+        <is>
+          <t>JiJieHao</t>
+        </is>
+      </c>
+      <c r="AT60" s="24" t="inlineStr">
+        <is>
+          <t>JiJieHao</t>
+        </is>
+      </c>
+      <c r="AU60" s="24" t="inlineStr">
+        <is>
+          <t>JiJieHao</t>
+        </is>
+      </c>
+      <c r="AV60" s="24" t="n"/>
+      <c r="AW60" s="24" t="n"/>
+      <c r="AX60" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY60" s="24" t="n"/>
+      <c r="AZ60" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA60" s="24" t="inlineStr">
+        <is>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
+        </is>
+      </c>
+      <c r="BB60" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC60" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD60" s="24" t="inlineStr">
+        <is>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
+        </is>
+      </c>
+      <c r="BE60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG60" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH60" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:39:32.209281Z</t>
+        </is>
+      </c>
+      <c r="BI60" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ60" s="25" t="n"/>
+      <c r="BK60" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL60" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM60" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN60" s="28" t="n"/>
+      <c r="BO60" s="28" t="n"/>
+      <c r="BP60" s="25" t="n"/>
+      <c r="BQ60" s="27" t="n"/>
+      <c r="BR60" s="28" t="n"/>
+      <c r="BS60" s="28" t="n"/>
+      <c r="BT60" s="28" t="n"/>
+      <c r="BU60" s="25" t="n"/>
+      <c r="BV60" s="29" t="n"/>
+      <c r="BW60" s="24" t="n"/>
+      <c r="BX60" s="30" t="n"/>
+      <c r="BY60" s="27" t="n"/>
+      <c r="BZ60" s="24" t="n"/>
+      <c r="CA60" s="31" t="n"/>
+      <c r="CB60" s="24" t="n"/>
+      <c r="CC60" s="24" t="n"/>
+      <c r="CD60" s="24" t="n"/>
+      <c r="CE60" s="24" t="n"/>
+      <c r="CF60" s="24" t="n"/>
+      <c r="CG60" s="24" t="n"/>
+      <c r="CH60" s="24" t="n"/>
+      <c r="CI60" s="24" t="n"/>
+      <c r="CJ60" s="24" t="n"/>
+      <c r="CK60" s="24" t="n"/>
+      <c r="CL60" s="24" t="n"/>
+      <c r="CM60" s="24" t="n"/>
+      <c r="CN60" s="24" t="n"/>
+      <c r="CO60" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO12" headerRowCount="1">
-  <autoFilter ref="A1:CO12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO18" headerRowCount="1">
+  <autoFilter ref="A1:CO18"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CO18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4143,22 +4143,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>f4ab16fa3d694661</t>
+          <t>d1b7bcbcd2784259</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-01T23:54:53.636521Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T00:30:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4193,49 +4193,69 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>223</v>
+        <v>-127</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>3.23</v>
+        <v>1.787402</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.53149</v>
+        <v>0.600127</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.221892</v>
+        <v>0.040656</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="S11" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
       <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:24.451346Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-spo-mars-2026-08-02).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4245,7 +4265,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4276,32 +4296,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4319,7 +4339,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>124bb01c66650940a67a9125e9f0677482f15aec343dc7b3e847d2027a63cccc</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4334,7 +4354,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>124bb01c66650940a67a9125e9f0677482f15aec343dc7b3e847d2027a63cccc</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4354,7 +4374,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:08.292176Z</t>
+          <t>2026-08-01T23:54:40.651895Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4364,19 +4384,23 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>223</v>
+        <v>-127</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>3.23</v>
+        <v>1.787402</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
       <c r="BU11" s="25" t="n"/>
@@ -4404,22 +4428,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>cdaa5ae202224ee4</t>
+          <t>61ee7f590c1941b2</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-02T07:16:24.505191Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T10:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>68255</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4429,12 +4453,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4454,26 +4478,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.543527</v>
+        <v>0.714955</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.033723</v>
+        <v>0.074667</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4496,7 +4520,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4537,32 +4561,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4580,7 +4604,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4595,7 +4619,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4615,7 +4639,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:12.835583Z</t>
+          <t>2026-08-02T07:16:02.743627Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4625,13 +4649,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4662,6 +4686,1572 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>bab01e5e88f24654</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>66809</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.531502</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.201469</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:03.217761Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>ce69e4af57c742bc</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>66836</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.690392</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.180588</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:04.165652Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>93872ba5754f4d78</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>68257</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.136729</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:06.663767Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>cfbfe29b7da64910</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69254</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.661873</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.032243</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:09.718841Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>9a1b1ea5c3124a98</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.06641</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:11.282396Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>ebfa53fe8c6c4b12</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.640064</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.140064</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:17.283191Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -4428,12 +4428,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>61ee7f590c1941b2</t>
+          <t>c66d7f408ffc42c6</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4478,23 +4478,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-178</v>
+        <v>-213</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.469484</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.680511</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.714955</v>
+        <v>0.714926</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.074667</v>
+        <v>0.034415</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>2</v>
@@ -4520,7 +4520,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:02.743627Z</t>
+          <t>2026-08-02T08:19:08.739294Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4649,13 +4649,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-178</v>
+        <v>-213</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.469484</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.680511</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4689,12 +4689,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>bab01e5e88f24654</t>
+          <t>29c4171eb02043a5</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4748,11 +4748,11 @@
         <v>0.330033</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.531502</v>
+        <v>0.531394</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.201469</v>
+        <v>0.201361</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>100</v>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:03.217761Z</t>
+          <t>2026-08-02T08:19:09.283371Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4950,12 +4950,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ce69e4af57c742bc</t>
+          <t>d5f6cb7d4ea245ba</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5009,11 +5009,11 @@
         <v>0.509804</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.690392</v>
+        <v>0.690561</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.180588</v>
+        <v>0.180757</v>
       </c>
       <c r="R14" s="26" t="n">
         <v>100</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:04.165652Z</t>
+          <t>2026-08-02T08:19:10.390430Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5211,12 +5211,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>93872ba5754f4d78</t>
+          <t>a3f58499dd6d4c06</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5261,23 +5261,23 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.676069</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.136729</v>
+        <v>0.166265</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>1.75</v>
@@ -5303,7 +5303,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:06.663767Z</t>
+          <t>2026-08-02T08:19:12.784904Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5432,13 +5432,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5472,12 +5472,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>cfbfe29b7da64910</t>
+          <t>e4990fed2bb6430d</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -5522,23 +5522,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.661873</v>
+        <v>0.662043</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.032243</v>
+        <v>0.042271</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.75</v>
@@ -5564,7 +5564,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:09.718841Z</t>
+          <t>2026-08-02T08:19:16.117377Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5693,13 +5693,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5733,12 +5733,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>9a1b1ea5c3124a98</t>
+          <t>9787fa9db23445ca</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5783,23 +5783,23 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.6664099999999999</v>
+        <v>0.66636</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.06641</v>
+        <v>0.056985</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1.75</v>
@@ -5825,7 +5825,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:11.282396Z</t>
+          <t>2026-08-02T08:19:17.713467Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5954,13 +5954,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5994,12 +5994,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>ebfa53fe8c6c4b12</t>
+          <t>ab595cea5fe44559</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6044,23 +6044,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2</v>
+        <v>1.819672</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.5</v>
+        <v>0.54955</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.640064</v>
+        <v>0.640228</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.140064</v>
+        <v>0.09067799999999999</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1.5</v>
@@ -6086,7 +6086,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:17.283191Z</t>
+          <t>2026-08-02T08:19:23.793481Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6215,13 +6215,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2</v>
+        <v>1.819672</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.5</v>
+        <v>0.54955</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO18" headerRowCount="1">
-  <autoFilter ref="A1:CO18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
+  <autoFilter ref="A1:CO15"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$18)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$18)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO18"/>
+  <dimension ref="A1:CO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4428,22 +4428,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>c66d7f408ffc42c6</t>
+          <t>871fce3506474811</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T10:30:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>66836</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4478,23 +4478,23 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-213</v>
+        <v>-104</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.961538</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.509804</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.714926</v>
+        <v>0.690561</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.034415</v>
+        <v>0.180757</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>2</v>
@@ -4520,7 +4520,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4561,32 +4561,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:08.739294Z</t>
+          <t>2026-08-02T09:59:44.064703Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4649,13 +4649,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-213</v>
+        <v>-104</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.961538</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.509804</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4689,22 +4689,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>29c4171eb02043a5</t>
+          <t>1266e5481bb746cc</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T13:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>68257</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J13" s="25" t="n"/>
@@ -4739,26 +4739,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>203</v>
+        <v>-113</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>3.03</v>
+        <v>1.884956</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.530516</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.531394</v>
+        <v>0.676069</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.201361</v>
+        <v>0.145553</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4822,32 +4822,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:09.283371Z</t>
+          <t>2026-08-02T09:59:46.682984Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4910,13 +4910,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>203</v>
+        <v>-113</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>3.03</v>
+        <v>1.884956</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.530516</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4950,22 +4950,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>d5f6cb7d4ea245ba</t>
+          <t>049e2112fd6048d2</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:30:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>66836</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5000,26 +5000,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-104</v>
+        <v>-156</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.641026</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.609375</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.690561</v>
+        <v>0.66636</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.180757</v>
+        <v>0.056985</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5083,32 +5083,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:10.390430Z</t>
+          <t>2026-08-02T09:59:51.297257Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5171,13 +5171,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-104</v>
+        <v>-156</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.641026</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.609375</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5211,22 +5211,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>a3f58499dd6d4c06</t>
+          <t>043ff069ee9a43ae</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5261,26 +5261,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.676069</v>
+        <v>0.640228</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.166265</v>
+        <v>0.09067799999999999</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5344,32 +5344,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:12.784904Z</t>
+          <t>2026-08-02T09:59:57.251438Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5432,13 +5432,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5469,789 +5469,6 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>e4990fed2bb6430d</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>69254</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>Honvéd</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.662043</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.042271</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>Honvéd</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>Honvéd</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>Honvéd</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:16.117377Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>9787fa9db23445ca</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>69263</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>ENJOY</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.66636</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>0.056985</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>48</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>ENJOY</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>ENJOY</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>ENJOY</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:17.713467Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>ab595cea5fe44559</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>67514</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M18" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N18" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O18" s="28" t="n">
-        <v>0.640228</v>
-      </c>
-      <c r="P18" s="28" t="n"/>
-      <c r="Q18" s="28" t="n">
-        <v>0.09067799999999999</v>
-      </c>
-      <c r="R18" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="S18" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T18" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF18" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG18" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH18" s="24" t="n"/>
-      <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
-      <c r="AK18" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL18" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN18" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO18" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP18" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AQ18" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AR18" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AS18" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AT18" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AU18" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AV18" s="24" t="n"/>
-      <c r="AW18" s="24" t="n"/>
-      <c r="AX18" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY18" s="24" t="n"/>
-      <c r="AZ18" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA18" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB18" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC18" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:23.793481Z</t>
-        </is>
-      </c>
-      <c r="BI18" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="25" t="n"/>
-      <c r="BK18" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL18" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM18" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN18" s="28" t="n"/>
-      <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
-      <c r="BS18" s="28" t="n"/>
-      <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
-      <c r="BV18" s="29" t="n"/>
-      <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n"/>
-      <c r="BY18" s="27" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
-      <c r="CB18" s="24" t="n"/>
-      <c r="CC18" s="24" t="n"/>
-      <c r="CD18" s="24" t="n"/>
-      <c r="CE18" s="24" t="n"/>
-      <c r="CF18" s="24" t="n"/>
-      <c r="CG18" s="24" t="n"/>
-      <c r="CH18" s="24" t="n"/>
-      <c r="CI18" s="24" t="n"/>
-      <c r="CJ18" s="24" t="n"/>
-      <c r="CK18" s="24" t="n"/>
-      <c r="CL18" s="24" t="n"/>
-      <c r="CM18" s="24" t="n"/>
-      <c r="CN18" s="24" t="n"/>
-      <c r="CO18" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
-  <autoFilter ref="A1:CO15"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP14" headerRowCount="1">
+  <autoFilter ref="A1:CP14"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO15"/>
+  <dimension ref="A1:CP14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2714,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2999,6 +3010,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3284,6 +3296,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3569,6 +3582,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3854,6 +3868,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4139,6 +4154,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4424,6 +4440,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4685,16 +4702,17 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>1266e5481bb746cc</t>
+          <t>1890098872ae4443</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4748,11 +4766,11 @@
         <v>0.530516</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.676069</v>
+        <v>0.67594</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.145553</v>
+        <v>0.145424</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>93</v>
@@ -4865,7 +4883,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4880,7 +4898,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4900,7 +4918,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:46.682984Z</t>
+          <t>2026-08-02T12:30:14.025736Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4946,16 +4964,17 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>049e2112fd6048d2</t>
+          <t>2dc39e41acdf4581</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5000,23 +5019,23 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-156</v>
+        <v>-170</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.588235</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.62963</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.66636</v>
+        <v>0.6659040000000001</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.056985</v>
+        <v>0.036274</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>1.75</v>
@@ -5042,7 +5061,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5126,7 +5145,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5141,7 +5160,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5161,7 +5180,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:51.297257Z</t>
+          <t>2026-08-02T13:07:36.093507Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5171,13 +5190,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-156</v>
+        <v>-170</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.588235</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.62963</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5207,267 +5226,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>043ff069ee9a43ae</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>67514</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.640228</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.09067799999999999</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T09:59:57.251438Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP14" headerRowCount="1">
-  <autoFilter ref="A1:CP14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP16" headerRowCount="1">
+  <autoFilter ref="A1:CP16"/>
   <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -753,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP14"/>
+  <dimension ref="A1:CP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4523,18 +4523,28 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W12" s="26" t="n"/>
       <c r="X12" s="26" t="n"/>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:33.702018Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
@@ -4683,7 +4693,11 @@
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
+      <c r="BW12" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX12" s="30" t="n"/>
       <c r="BY12" s="27" t="n"/>
       <c r="BZ12" s="24" t="n"/>
@@ -4969,12 +4983,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>2dc39e41acdf4581</t>
+          <t>7c8a11062be44bbf</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -4984,7 +4998,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>69263</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4994,12 +5008,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5019,23 +5033,23 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.6659040000000001</v>
+        <v>0.653037</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.036274</v>
+        <v>0.043662</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>1.75</v>
@@ -5061,7 +5075,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-for-lk-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5102,32 +5116,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5145,7 +5159,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5160,7 +5174,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5180,7 +5194,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:36.093507Z</t>
+          <t>2026-08-02T15:51:25.435587Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5190,13 +5204,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5226,7 +5240,543 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="n"/>
+      <c r="CP14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>4a9cb06be6c94e51</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.599394</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.019562</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:31.676274Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>700b618c42d4405b</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.6819730000000001</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.041685</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:37.423413Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP16" headerRowCount="1">
-  <autoFilter ref="A1:CP16"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
+  <autoFilter ref="A1:CQ15"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP16"/>
+  <dimension ref="A1:CQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3297,6 +3309,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3583,6 +3596,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3869,6 +3883,7 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4155,6 +4170,7 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4441,6 +4457,7 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4717,6 +4734,7 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4979,26 +4997,27 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>7c8a11062be44bbf</t>
+          <t>a975e837b88c43d8</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5008,12 +5027,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5023,7 +5042,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5033,26 +5052,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.653037</v>
+        <v>0.599195</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.043662</v>
+        <v>0.019363</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5075,7 +5094,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-for-lk-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5116,32 +5135,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5159,7 +5178,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5174,7 +5193,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5194,7 +5213,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:25.435587Z</t>
+          <t>2026-08-02T16:15:04.678326Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5204,13 +5223,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-156</v>
+        <v>-138</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.724638</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.579832</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5240,7 +5259,8 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
-      <c r="CP14" s="24" t="inlineStr">
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5249,22 +5269,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>4a9cb06be6c94e51</t>
+          <t>4c4413651a2a4ceb</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>69268</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5274,12 +5294,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5299,26 +5319,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-138</v>
+        <v>-178</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.561798</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.640288</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.599394</v>
+        <v>0.662883</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.019562</v>
+        <v>0.022595</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5341,7 +5361,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5382,32 +5402,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5425,7 +5445,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5440,7 +5460,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5460,7 +5480,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:31.676274Z</t>
+          <t>2026-08-02T16:15:10.799851Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5470,13 +5490,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-138</v>
+        <v>-178</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.561798</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.640288</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5506,273 +5526,8 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>700b618c42d4405b</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.6819730000000001</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.041685</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T15:51:37.423413Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="inlineStr">
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
-  <autoFilter ref="A1:CQ15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
+  <autoFilter ref="A1:CQ16"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ15"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5002,22 +5002,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>a975e837b88c43d8</t>
+          <t>d46b1c6c074d4d79</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5052,26 +5052,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-138</v>
+        <v>-194</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.515464</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.659864</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.599195</v>
+        <v>0.68024</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.019363</v>
+        <v>0.020376</v>
       </c>
       <c r="R14" s="26" t="n">
         <v>30</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5135,32 +5135,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:04.678326Z</t>
+          <t>2026-08-02T16:53:19.829844Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5223,13 +5223,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-138</v>
+        <v>-194</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.515464</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.659864</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5269,22 +5269,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>4c4413651a2a4ceb</t>
+          <t>b0445f7352d444ff</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5319,26 +5319,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-178</v>
+        <v>-138</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.724638</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.579832</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.662883</v>
+        <v>0.599198</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.022595</v>
+        <v>0.019366</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5402,32 +5402,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:10.799851Z</t>
+          <t>2026-08-02T16:53:25.545768Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5490,13 +5490,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-178</v>
+        <v>-138</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.724638</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.579832</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5533,6 +5533,273 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>0797e5dac5e74572</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:33.678893Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.663025</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.022737</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:29.527479Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
-  <autoFilter ref="A1:CQ16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ14" headerRowCount="1">
+  <autoFilter ref="A1:CQ14"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ16"/>
+  <dimension ref="A1:CQ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5266,540 +5266,6 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>b0445f7352d444ff</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>68289</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.599198</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.019366</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:25.545768Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>0797e5dac5e74572</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.663025</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.022737</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:29.527479Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ14" headerRowCount="1">
-  <autoFilter ref="A1:CQ14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
+  <autoFilter ref="A1:CQ16"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ14"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5266,6 +5266,540 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>527b87d97fca4de2</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.599199</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.019367</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:31.821007Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>50897d877f614f10</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.663041</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.022753</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.924167Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ16" headerRowCount="1">
-  <autoFilter ref="A1:CQ16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
+  <autoFilter ref="A1:CQ17"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ16"/>
+  <dimension ref="A1:CQ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5269,12 +5269,12 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>527b87d97fca4de2</t>
+          <t>936b606e7d544e3c</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:31.821007Z</t>
+          <t>2026-08-02T18:08:46.352076Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5536,22 +5536,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>50897d877f614f10</t>
+          <t>db1dc943d75f40cf</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5586,26 +5586,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.663041</v>
+        <v>0.639896</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.022753</v>
+        <v>0.020124</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5669,32 +5669,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:36.924167Z</t>
+          <t>2026-08-02T18:08:48.789246Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5757,13 +5757,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5800,6 +5800,273 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>d60a6e820d4f4adc</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:55.998248Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.663041</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.022753</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.418739Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
-  <autoFilter ref="A1:CQ17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ14" headerRowCount="1">
+  <autoFilter ref="A1:CQ14"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ17"/>
+  <dimension ref="A1:CQ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5266,807 +5266,6 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>936b606e7d544e3c</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>68289</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.599199</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.019367</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:46.352076Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>db1dc943d75f40cf</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>67514</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M16" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N16" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O16" s="28" t="n">
-        <v>0.639896</v>
-      </c>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n">
-        <v>0.020124</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S16" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF16" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG16" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH16" s="24" t="n"/>
-      <c r="AI16" s="31" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL16" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN16" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO16" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP16" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AQ16" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AR16" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AS16" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AT16" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AU16" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AV16" s="24" t="n"/>
-      <c r="AW16" s="24" t="n"/>
-      <c r="AX16" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY16" s="24" t="n"/>
-      <c r="AZ16" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA16" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB16" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:48.789246Z</t>
-        </is>
-      </c>
-      <c r="BI16" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="25" t="n"/>
-      <c r="BK16" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL16" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM16" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN16" s="28" t="n"/>
-      <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
-      <c r="BS16" s="28" t="n"/>
-      <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
-      <c r="BV16" s="29" t="n"/>
-      <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n"/>
-      <c r="BY16" s="27" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
-      <c r="CB16" s="24" t="n"/>
-      <c r="CC16" s="24" t="n"/>
-      <c r="CD16" s="24" t="n"/>
-      <c r="CE16" s="24" t="n"/>
-      <c r="CF16" s="24" t="n"/>
-      <c r="CG16" s="24" t="n"/>
-      <c r="CH16" s="24" t="n"/>
-      <c r="CI16" s="24" t="n"/>
-      <c r="CJ16" s="24" t="n"/>
-      <c r="CK16" s="24" t="n"/>
-      <c r="CL16" s="24" t="n"/>
-      <c r="CM16" s="24" t="n"/>
-      <c r="CN16" s="24" t="n"/>
-      <c r="CO16" s="24" t="n"/>
-      <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>d60a6e820d4f4adc</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M17" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N17" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O17" s="28" t="n">
-        <v>0.663041</v>
-      </c>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n">
-        <v>0.022753</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S17" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U17" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF17" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG17" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH17" s="24" t="n"/>
-      <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
-      <c r="AK17" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN17" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP17" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ17" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR17" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS17" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT17" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU17" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV17" s="24" t="n"/>
-      <c r="AW17" s="24" t="n"/>
-      <c r="AX17" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY17" s="24" t="n"/>
-      <c r="AZ17" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA17" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB17" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:51.418739Z</t>
-        </is>
-      </c>
-      <c r="BI17" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="25" t="n"/>
-      <c r="BK17" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL17" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM17" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN17" s="28" t="n"/>
-      <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
-      <c r="BS17" s="28" t="n"/>
-      <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
-      <c r="BV17" s="29" t="n"/>
-      <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n"/>
-      <c r="BY17" s="27" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
-      <c r="CB17" s="24" t="n"/>
-      <c r="CC17" s="24" t="n"/>
-      <c r="CD17" s="24" t="n"/>
-      <c r="CE17" s="24" t="n"/>
-      <c r="CF17" s="24" t="n"/>
-      <c r="CG17" s="24" t="n"/>
-      <c r="CH17" s="24" t="n"/>
-      <c r="CI17" s="24" t="n"/>
-      <c r="CJ17" s="24" t="n"/>
-      <c r="CK17" s="24" t="n"/>
-      <c r="CL17" s="24" t="n"/>
-      <c r="CM17" s="24" t="n"/>
-      <c r="CN17" s="24" t="n"/>
-      <c r="CO17" s="24" t="n"/>
-      <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ14" headerRowCount="1">
-  <autoFilter ref="A1:CQ14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
+  <autoFilter ref="A1:CQ17"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$17)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$17)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ14"/>
+  <dimension ref="A1:CQ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5266,6 +5266,807 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>95d87d5169fc4ae9</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.599274</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.019442</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:35.118991Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>252f5baff6014e4d</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.640004</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.020232</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:37.624827Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2965fad2679e43bb</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.663166</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.022878</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.237935Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ17" headerRowCount="1">
-  <autoFilter ref="A1:CQ17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ21" headerRowCount="1">
+  <autoFilter ref="A1:CQ21"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$17)</f>
+        <f>COUNTA('Picks'!$A$2:$A$21)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$17,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")/(COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"win")+COUNTIFS('Picks'!$BX$2:$BX$17,"&gt;0",'Picks'!$V$2:$V$17,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$17)/SUM('Picks'!$BX$2:$BX$17),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$17)</f>
+        <f>SUM('Picks'!$BY$2:$BY$21)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$17,"&lt;&gt;",'Picks'!$AB$2:$AB$17),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$17,'Picks'!$AM$2:$AM$17,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A14,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A15,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled",'Picks'!$V$2:$V$17,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$17,'Picks'!$H$2:$H$17,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$17,'Picks'!$H$2:$H$17,$A16,'Picks'!$U$2:$U$17,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ17"/>
+  <dimension ref="A1:CQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4817,18 +4817,28 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W13" s="26" t="n"/>
       <c r="X13" s="26" t="n"/>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:48.118824Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
@@ -4977,7 +4987,11 @@
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
+      <c r="BW13" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX13" s="30" t="n"/>
       <c r="BY13" s="27" t="n"/>
       <c r="BZ13" s="24" t="n"/>
@@ -5080,18 +5094,28 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W14" s="26" t="n"/>
       <c r="X14" s="26" t="n"/>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:49.249923Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
@@ -5240,7 +5264,11 @@
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
-      <c r="BW14" s="24" t="n"/>
+      <c r="BW14" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX14" s="30" t="n"/>
       <c r="BY14" s="27" t="n"/>
       <c r="BZ14" s="24" t="n"/>
@@ -5269,22 +5297,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>95d87d5169fc4ae9</t>
+          <t>3e5ca2341bea45d1</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:44.992034Z</t>
+          <t>2026-08-03T10:14:59.378487Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5294,12 +5322,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5319,26 +5347,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-138</v>
+        <v>-156</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.641026</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.609375</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.599274</v>
+        <v>0.639821</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.019442</v>
+        <v>0.030446</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5347,21 +5375,41 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:35.671440Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5402,32 +5450,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5445,7 +5493,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5460,7 +5508,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>a67b482e0cc299818c9d6a6183162092d6b3cbeea4f974054606da1c44c3bd99</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5480,7 +5528,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:35.118991Z</t>
+          <t>2026-08-03T10:14:38.370048Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5490,19 +5538,23 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-138</v>
+        <v>-156</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.641026</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.609375</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5536,22 +5588,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>252f5baff6014e4d</t>
+          <t>02ebc095ca494cd9</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:44.992034Z</t>
+          <t>2026-08-03T19:54:57.645683Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T21:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>70532</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5561,12 +5613,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5586,23 +5638,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.640004</v>
+        <v>0.6304380000000001</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.020232</v>
+        <v>0.030438</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.5</v>
@@ -5628,7 +5680,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-odk-reda-2026-08-03).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5669,32 +5721,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5712,7 +5764,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5727,7 +5779,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>49e72bc47e8b746259057b18a0727b3402ae02f53069edfae5b6532757438c2c</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5747,7 +5799,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:37.624827Z</t>
+          <t>2026-08-03T19:54:46.268393Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5757,13 +5809,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.666667</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5803,22 +5855,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>2965fad2679e43bb</t>
+          <t>35497da3e6964fbc</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:44.992034Z</t>
+          <t>2026-08-04T02:01:00.694416Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-04T11:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5828,12 +5880,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5853,26 +5905,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-178</v>
+        <v>117</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.17</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.460829</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.663166</v>
+        <v>0.551006</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.022878</v>
+        <v>0.09017699999999999</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5895,7 +5947,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5936,32 +5988,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5979,7 +6031,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5994,7 +6046,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6014,7 +6066,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:24:40.237935Z</t>
+          <t>2026-08-04T02:00:44.822978Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6024,13 +6076,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-178</v>
+        <v>117</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.17</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.460829</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6067,6 +6119,1074 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>5917a6df4bb84597</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:01:00.694416Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Betclic Apogee Esports</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Acend</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.691599</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.111767</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ace-bca-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Betclic Apogee Esports</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Betclic Apogee Esports</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Betclic Apogee Esports</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Acend</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Acend</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Acend</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:45.360175Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>34e51feb042b446f</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:01:00.694416Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Drama eSports</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>KUUSAMO.gg</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.576412</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.066608</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ksm-drama-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Drama eSports</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Drama eSports</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Drama eSports</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>KUUSAMO.gg</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>KUUSAMO.gg</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>KUUSAMO.gg</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:54.911657Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>bb3993ce6e8547e3</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:01:00.694416Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Subtop De France</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.598969</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.08916499999999999</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-gel-sdf-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Subtop De France</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Subtop De France</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Subtop De France</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Glitchtech Esports</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:57.015430Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>d6d17593ded54c73</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T04:00:12.475882Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.67501</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.055238</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T04:00:07.463015Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ21" headerRowCount="1">
-  <autoFilter ref="A1:CQ21"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR23" headerRowCount="1">
+  <autoFilter ref="A1:CR23"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$21)</f>
+        <f>COUNTA('Picks'!$A$2:$A$23)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$21)</f>
+        <f>SUM('Picks'!$BY$2:$BY$23)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ21"/>
+  <dimension ref="A1:CR23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3310,6 +3322,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3597,6 +3610,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3884,6 +3898,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4171,6 +4186,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4458,6 +4474,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4735,6 +4752,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5012,6 +5030,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5288,7 +5307,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5579,7 +5599,8 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5846,7 +5867,8 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5855,12 +5877,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>35497da3e6964fbc</t>
+          <t>e17b52861cea4d2b</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5905,23 +5927,23 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.490196</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.551006</v>
+        <v>0.551011</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.09017699999999999</v>
+        <v>0.060815</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1</v>
@@ -5947,7 +5969,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6031,7 +6053,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6046,7 +6068,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6066,7 +6088,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:44.822978Z</t>
+          <t>2026-08-04T08:56:24.737438Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6076,13 +6098,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.490196</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6113,7 +6135,8 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6122,12 +6145,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>5917a6df4bb84597</t>
+          <t>c8aec1582044472d</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6181,11 +6204,11 @@
         <v>0.579832</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.691599</v>
+        <v>0.691594</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.111767</v>
+        <v>0.111762</v>
       </c>
       <c r="R18" s="26" t="n">
         <v>76</v>
@@ -6298,7 +6321,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6313,7 +6336,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6333,7 +6356,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:45.360175Z</t>
+          <t>2026-08-04T08:56:25.971824Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6380,7 +6403,8 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6389,12 +6413,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>34e51feb042b446f</t>
+          <t>efd095faf17a4246</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6404,7 +6428,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>71385</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6414,12 +6438,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6448,17 +6472,17 @@
         <v>0.509804</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.576412</v>
+        <v>0.698419</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.066608</v>
+        <v>0.188615</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6481,7 +6505,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ksm-drama-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6522,32 +6546,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6565,7 +6589,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6580,7 +6604,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6600,7 +6624,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:54.911657Z</t>
+          <t>2026-08-04T08:56:41.500495Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6647,7 +6671,8 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6656,12 +6681,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>bb3993ce6e8547e3</t>
+          <t>888b9397584e4826</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6671,7 +6696,7 @@
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>71390</t>
+          <t>71388</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6681,12 +6706,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6696,7 +6721,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6706,26 +6731,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.884956</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.530516</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.598969</v>
+        <v>0.556222</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.08916499999999999</v>
+        <v>0.025706</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6748,7 +6773,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-gel-sdf-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6789,32 +6814,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6832,7 +6857,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6847,7 +6872,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6867,7 +6892,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:57.015430Z</t>
+          <t>2026-08-04T08:56:42.051951Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6877,13 +6902,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.884956</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.530516</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6914,7 +6939,8 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6923,12 +6949,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>d6d17593ded54c73</t>
+          <t>fabc435dc6344b39</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T04:00:12.475882Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6938,7 +6964,7 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71387</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6948,12 +6974,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6963,7 +6989,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -6973,26 +6999,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-163</v>
+        <v>-144</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.694444</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.590164</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.67501</v>
+        <v>0.6138</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.055238</v>
+        <v>0.023636</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7015,7 +7041,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7056,32 +7082,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7099,7 +7125,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7114,7 +7140,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7134,7 +7160,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T04:00:07.463015Z</t>
+          <t>2026-08-04T08:56:42.609865Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7144,13 +7170,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-163</v>
+        <v>-144</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.694444</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.590164</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7181,7 +7207,544 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>9ccb18b3fc594980</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.67501</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.084846</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:43.095313Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>c7553372da784bd9</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.6268860000000001</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.017511</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-gea-navij-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.829078Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR23" headerRowCount="1">
-  <autoFilter ref="A1:CR23"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
+  <autoFilter ref="A1:CS25"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$23)</f>
+        <f>COUNTA('Picks'!$A$2:$A$25)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$23)</f>
+        <f>SUM('Picks'!$BY$2:$BY$25)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR23"/>
+  <dimension ref="A1:CS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3323,6 +3335,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3611,6 +3624,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3899,6 +3913,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4187,6 +4202,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4475,6 +4491,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4753,6 +4770,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5031,6 +5049,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5308,7 +5327,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5600,7 +5620,8 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5868,7 +5889,8 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5955,18 +5977,38 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:59.228709Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
@@ -6109,8 +6151,12 @@
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6136,7 +6182,8 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6223,18 +6270,38 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:00.544032Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ace-bca-2026-08-04).</t>
@@ -6247,7 +6314,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6377,8 +6444,12 @@
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6404,7 +6475,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6413,22 +6485,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>efd095faf17a4246</t>
+          <t>6683be048cab49e5</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:30:00Z</t>
+          <t>2026-08-04T17:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6438,12 +6510,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6463,26 +6535,26 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.698419</v>
+        <v>0.571449</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.188615</v>
+        <v>0.021899</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6505,7 +6577,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-for-agc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6546,32 +6618,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6589,7 +6661,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6604,7 +6676,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6624,7 +6696,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:41.500495Z</t>
+          <t>2026-08-04T14:26:42.351782Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6634,13 +6706,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6672,7 +6744,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6681,22 +6754,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>888b9397584e4826</t>
+          <t>3fb6607edd904d03</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:30:00Z</t>
+          <t>2026-08-04T17:15:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>71388</t>
+          <t>71339</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6706,12 +6779,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6721,7 +6794,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6731,26 +6804,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-113</v>
+        <v>-203</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.492611</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.669967</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.556222</v>
+        <v>0.681734</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.025706</v>
+        <v>0.011767</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6773,7 +6846,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-xi-oldboyspl-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6814,32 +6887,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6857,7 +6930,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6872,7 +6945,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6892,7 +6965,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:42.051951Z</t>
+          <t>2026-08-04T14:26:44.028305Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6902,13 +6975,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-113</v>
+        <v>-203</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.492611</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.669967</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6940,7 +7013,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6949,12 +7023,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>fabc435dc6344b39</t>
+          <t>93e601c336a54c31</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6964,7 +7038,7 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71382</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6974,12 +7048,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6989,7 +7063,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -7008,17 +7082,17 @@
         <v>0.590164</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.6138</v>
+        <v>0.67486</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.023636</v>
+        <v>0.08469599999999999</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7041,7 +7115,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7082,32 +7156,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7125,7 +7199,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7140,7 +7214,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7160,7 +7234,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:42.609865Z</t>
+          <t>2026-08-04T14:26:45.147234Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7208,7 +7282,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7217,12 +7292,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>9ccb18b3fc594980</t>
+          <t>4feb73288bdc4623</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7232,7 +7307,7 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7242,12 +7317,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7267,23 +7342,23 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.694444</v>
+        <v>2</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.67501</v>
+        <v>0.645876</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.084846</v>
+        <v>0.145876</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="S22" s="29" t="n">
         <v>1.75</v>
@@ -7309,7 +7384,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-fla-agc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7350,32 +7425,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7393,7 +7468,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7408,7 +7483,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7428,7 +7503,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:43.095313Z</t>
+          <t>2026-08-04T14:26:46.831301Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7438,13 +7513,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.694444</v>
+        <v>2</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7476,7 +7551,8 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7485,22 +7561,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>c7553372da784bd9</t>
+          <t>eeec8b8412654053</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T14:00:00Z</t>
+          <t>2026-08-04T18:30:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>71388</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7510,12 +7586,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>GamersLab Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7525,7 +7601,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7535,26 +7611,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-156</v>
+        <v>-108</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.925926</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.519231</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.6268860000000001</v>
+        <v>0.556024</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.017511</v>
+        <v>0.036793</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7577,7 +7653,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-gea-navij-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7618,32 +7694,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>GamersLab Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>GamersLab Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>GamersLab Esports</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7661,7 +7737,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7676,7 +7752,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7696,7 +7772,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:52.829078Z</t>
+          <t>2026-08-04T14:26:48.498248Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7706,13 +7782,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-156</v>
+        <v>-108</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.925926</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.519231</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7744,7 +7820,546 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>c5c573ac5be14f59</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:03.198804Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Arch</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.698177</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.198177</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Banger Gang</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Arch</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Arch</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Arch</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:49.093007Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>eb5c0f2876c14b6b</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:03.198804Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.614141</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.034309</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.211130Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
-  <autoFilter ref="A1:CS25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
+  <autoFilter ref="A1:CS29"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$25)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$25)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS25"/>
+  <dimension ref="A1:CS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5708,18 +5708,38 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:35.233639Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-odk-reda-2026-08-03).</t>
@@ -5862,8 +5882,12 @@
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -6485,12 +6509,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>6683be048cab49e5</t>
+          <t>c8987915a30b4168</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T16:54:42.280324Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6535,49 +6559,69 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.571449</v>
+        <v>0.580391</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.021899</v>
+        <v>0.02092</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:49.354797Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-for-agc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-for-agc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6661,7 +6705,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6671,12 +6715,12 @@
       </c>
       <c r="BC19" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>87e73f3e8c33751dbc7005b4404d0ee0ac9b9f8c3869a8f2e7fbc367004c2f64</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6691,12 +6735,12 @@
       </c>
       <c r="BG19" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:42.351782Z</t>
+          <t>2026-08-04T16:54:14.340644Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6706,19 +6750,23 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.787402</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
       <c r="BU19" s="25" t="n"/>
@@ -6754,22 +6802,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>3fb6607edd904d03</t>
+          <t>c1476e72f76d4983</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T18:08:37.067138Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T17:15:00Z</t>
+          <t>2026-08-04T18:30:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>71339</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6779,12 +6827,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6794,7 +6842,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6804,49 +6852,69 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-203</v>
+        <v>-127</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.787402</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.681734</v>
+        <v>0.633669</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.011767</v>
+        <v>0.074198</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:01.153467Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-xi-oldboyspl-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-fla-agc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6856,7 +6924,7 @@
       </c>
       <c r="AG20" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH20" s="24" t="n"/>
@@ -6887,32 +6955,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>FAST LAYNERS</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6930,7 +6998,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6940,12 +7008,12 @@
       </c>
       <c r="BC20" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6960,12 +7028,12 @@
       </c>
       <c r="BG20" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:44.028305Z</t>
+          <t>2026-08-04T18:08:12.712388Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6975,19 +7043,23 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-203</v>
+        <v>-127</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.787402</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7023,12 +7095,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>93e601c336a54c31</t>
+          <t>4ca8334d2c034365</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T18:08:37.067138Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7038,7 +7110,7 @@
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7048,12 +7120,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -7073,49 +7145,69 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-144</v>
+        <v>-104</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.961538</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.509804</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.67486</v>
+        <v>0.684275</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.08469599999999999</v>
+        <v>0.174471</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:06:37.190424Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7125,7 +7217,7 @@
       </c>
       <c r="AG21" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH21" s="24" t="n"/>
@@ -7156,32 +7248,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7199,7 +7291,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7209,12 +7301,12 @@
       </c>
       <c r="BC21" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7229,12 +7321,12 @@
       </c>
       <c r="BG21" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:45.147234Z</t>
+          <t>2026-08-04T18:08:14.227023Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7244,19 +7336,23 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-144</v>
+        <v>-104</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.961538</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.509804</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7292,12 +7388,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>4feb73288bdc4623</t>
+          <t>a3bc7316012e44cf</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T18:08:37.067138Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7307,7 +7403,7 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>71391</t>
+          <t>71388</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7317,12 +7413,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>FAST LAYNERS</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7342,49 +7438,69 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2</v>
+        <v>1.884956</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.5</v>
+        <v>0.530516</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.645876</v>
+        <v>0.556272</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.145876</v>
+        <v>0.025756</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:03.473429Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-fla-agc-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7425,32 +7541,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>A Great Chaos</t>
+          <t>Fraternity</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>FAST LAYNERS</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>FAST LAYNERS</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>FAST LAYNERS</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7468,7 +7584,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7478,12 +7594,12 @@
       </c>
       <c r="BC22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7498,12 +7614,12 @@
       </c>
       <c r="BG22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:46.831301Z</t>
+          <t>2026-08-04T18:08:15.431614Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7513,19 +7629,23 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2</v>
+        <v>1.884956</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.5</v>
+        <v>0.530516</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
       <c r="BU22" s="25" t="n"/>
@@ -7561,12 +7681,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>eeec8b8412654053</t>
+          <t>0ec6b33176e14a00</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T18:08:37.067138Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7576,7 +7696,7 @@
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>71388</t>
+          <t>71387</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7586,12 +7706,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7601,7 +7721,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7611,30 +7731,30 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.724638</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.579832</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.556024</v>
+        <v>0.595428</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.036793</v>
+        <v>0.015596</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U23" s="24" t="inlineStr">
@@ -7653,7 +7773,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7694,32 +7814,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>OLDBOYS PL</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>eSuba</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7737,7 +7857,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7747,12 +7867,12 @@
       </c>
       <c r="BC23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7767,12 +7887,12 @@
       </c>
       <c r="BG23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:48.498248Z</t>
+          <t>2026-08-04T18:08:16.175127Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7782,13 +7902,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.724638</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.579832</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7830,12 +7950,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>c5c573ac5be14f59</t>
+          <t>b9491e32cfde4c99</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-04T18:08:37.067138Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7845,7 +7965,7 @@
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>71382</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7855,12 +7975,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7880,49 +8000,69 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.5</v>
+        <v>0.460829</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.698177</v>
+        <v>0.674864</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.198177</v>
+        <v>0.214035</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:05.758684Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7932,7 +8072,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -7963,32 +8103,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>JUMBO TEAM</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8006,7 +8146,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8016,12 +8156,12 @@
       </c>
       <c r="BC24" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>3d3dc6a4f0641cb9aa015aaf4ccd2f260230dfea2e1b613f3ccdb860b2230f3e</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8036,12 +8176,12 @@
       </c>
       <c r="BG24" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:49.093007Z</t>
+          <t>2026-08-04T18:08:19.220614Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8051,19 +8191,23 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.5</v>
+        <v>0.460829</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8099,22 +8243,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>eb5c0f2876c14b6b</t>
+          <t>14721795855848fd</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:27:03.198804Z</t>
+          <t>2026-08-05T04:39:04.512717Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:30:00Z</t>
+          <t>2026-08-05T10:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71795</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8124,12 +8268,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>Betclic Apogee Esports</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8139,7 +8283,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8149,30 +8293,30 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-138</v>
+        <v>156</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.56</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.390625</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.614141</v>
+        <v>0.5349</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.034309</v>
+        <v>0.144275</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U25" s="24" t="inlineStr">
@@ -8191,7 +8335,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-js-bca-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8232,32 +8376,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>Betclic Apogee Esports</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>Betclic Apogee Esports</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>OLDBOYS PL</t>
+          <t>Betclic Apogee Esports</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>eSuba</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8275,7 +8419,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8285,12 +8429,12 @@
       </c>
       <c r="BC25" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8305,12 +8449,12 @@
       </c>
       <c r="BG25" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v5</t>
+          <t>cs2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:50.211130Z</t>
+          <t>2026-08-05T04:38:15.635268Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8320,13 +8464,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-138</v>
+        <v>156</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.56</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.390625</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8365,6 +8509,1082 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>4e180e0f330b4726</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:04.512717Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>72488</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nordic Partners Gaming </t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.6973470000000001</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.02738</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-npg-g1-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>GenOne</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nordic Partners Gaming </t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nordic Partners Gaming </t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nordic Partners Gaming </t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:28.087442Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>b705e0f1ebb449bf</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:04.512717Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>72533</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>XI Esport</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Esport BERG</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.63446</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.18401</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-berg-xi-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>XI Esport</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>XI Esport</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>XI Esport</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Esport BERG</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Esport BERG</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Esport BERG</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:29.742606Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>e57dee7b2aee4309</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:04.512717Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.606734</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>0.166205</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-pcific-ttbs-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:44.309251Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>61896a12a7194a73</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:39:04.512717Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.6083229999999999</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.037508</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-era-efa-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:48.579124Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
-  <autoFilter ref="A1:CS29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS33" headerRowCount="1">
+  <autoFilter ref="A1:CS33"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$29)</f>
+        <f>COUNTA('Picks'!$A$2:$A$33)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$33,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$33,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")+COUNTIFS('Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$33,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")/(COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")+COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$33)/SUM('Picks'!$BX$2:$BX$33),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$29)</f>
+        <f>SUM('Picks'!$BY$2:$BY$33)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$33,"&lt;&gt;",'Picks'!$AB$2:$AB$33),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$33,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$33,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$33,'Picks'!$AM$2:$AM$33,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS29"/>
+  <dimension ref="A1:CS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8321,18 +8321,38 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:52.669190Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-js-bca-2026-08-05).</t>
@@ -8345,7 +8365,7 @@
       </c>
       <c r="AG25" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH25" s="24" t="n"/>
@@ -8475,8 +8495,12 @@
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8512,22 +8536,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>4e180e0f330b4726</t>
+          <t>9c70e97e2fa54b07</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:04.512717Z</t>
+          <t>2026-08-05T13:56:36.539226Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T14:00:00Z</t>
+          <t>2026-08-05T16:30:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>72488</t>
+          <t>72533</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8537,12 +8561,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic Partners Gaming </t>
+          <t>Esport BERG</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8552,7 +8576,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8562,26 +8586,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-203</v>
+        <v>138</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.38</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.420168</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.6973470000000001</v>
+        <v>0.633758</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.02738</v>
+        <v>0.21359</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8604,7 +8628,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-npg-g1-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-berg-xi-2026-08-05).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8645,32 +8669,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>XI Esport</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic Partners Gaming </t>
+          <t>Esport BERG</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic Partners Gaming </t>
+          <t>Esport BERG</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic Partners Gaming </t>
+          <t>Esport BERG</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8688,7 +8712,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8703,7 +8727,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8723,7 +8747,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:28.087442Z</t>
+          <t>2026-08-05T13:56:11.868130Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8733,13 +8757,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-203</v>
+        <v>138</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.38</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.420168</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8781,22 +8805,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>b705e0f1ebb449bf</t>
+          <t>f3cf5ec67dea499b</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:04.512717Z</t>
+          <t>2026-08-05T13:56:36.539226Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30:00Z</t>
+          <t>2026-08-05T17:00:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>72533</t>
+          <t>72534</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8806,12 +8830,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>Spirit Academy Green</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Esport BERG</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8831,26 +8855,26 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2.22</v>
+        <v>1.588235</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.62963</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.63446</v>
+        <v>0.647084</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.18401</v>
+        <v>0.017454</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -8873,7 +8897,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-berg-xi-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-falf-sag-2026-08-05).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8914,32 +8938,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>Spirit Academy Green</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>Spirit Academy Green</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>XI Esport</t>
+          <t>Spirit Academy Green</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>Esport BERG</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>Esport BERG</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>Esport BERG</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8957,7 +8981,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8972,7 +8996,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8992,7 +9016,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:29.742606Z</t>
+          <t>2026-08-05T13:56:13.589736Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9002,13 +9026,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>2.22</v>
+        <v>1.588235</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.62963</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9050,22 +9074,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>e57dee7b2aee4309</t>
+          <t>590bc13276b8452a</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:04.512717Z</t>
+          <t>2026-08-05T13:56:36.539226Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T08:00:00Z</t>
+          <t>2026-08-05T18:30:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>70562</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -9075,12 +9099,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9100,26 +9124,26 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.606734</v>
+        <v>0.748624</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.166205</v>
+        <v>0.267855</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9142,7 +9166,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-pcific-ttbs-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-pure-drama-2026-08-05).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9183,32 +9207,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>PURE</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9226,7 +9250,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9241,7 +9265,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9261,7 +9285,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:44.309251Z</t>
+          <t>2026-08-05T13:56:19.555277Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9271,13 +9295,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.480769</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9319,22 +9343,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>61896a12a7194a73</t>
+          <t>ca5840fb1db34889</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:39:04.512717Z</t>
+          <t>2026-08-05T13:56:36.539226Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:30:00Z</t>
+          <t>2026-08-06T08:00:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9344,12 +9368,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9369,26 +9393,26 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-133</v>
+        <v>138</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.38</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.420168</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.6083229999999999</v>
+        <v>0.530945</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.037508</v>
+        <v>0.110777</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9411,7 +9435,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-era-efa-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-lav-bpl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9452,32 +9476,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9495,7 +9519,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9510,7 +9534,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>79b38f494ba89a56e3ba1ee48b9a2a5937958160c434a13516c1eb8ec97a91aa</t>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9530,7 +9554,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:48.579124Z</t>
+          <t>2026-08-05T13:56:22.532084Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9540,13 +9564,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-133</v>
+        <v>138</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.38</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.420168</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9585,6 +9609,1082 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>502da86df76d4f01</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:36.539226Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>70562</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.606164</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.155714</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>98</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-pcific-ttbs-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>WRAITH PCIFIC</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:23.683454Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>db86a6b057344de5</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:36.539226Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>70787</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.607715</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-era-efa-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire Academy</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:26.353887Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>990e0ba190de46ce</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:36.539226Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>72651</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Yawara Esports</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Isurus</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.746375</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.146375</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-isg-yaw-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Yawara Esports</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Yawara Esports</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Yawara Esports</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Isurus</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Isurus</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Isurus</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:34.073375Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>d89c179c211c48b3</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:36.539226Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>72652</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.543196</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.092746</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-mw-pcy-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Procyon Gaming</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:56:35.923759Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS33" headerRowCount="1">
-  <autoFilter ref="A1:CS33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS36" headerRowCount="1">
+  <autoFilter ref="A1:CS36"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$33)</f>
+        <f>COUNTA('Picks'!$A$2:$A$36)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$33,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$36,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$33,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")+COUNTIFS('Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$33,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$36,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")/(COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"win")+COUNTIFS('Picks'!$BX$2:$BX$33,"&gt;0",'Picks'!$V$2:$V$33,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")/(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$33)/SUM('Picks'!$BX$2:$BX$33),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$36)/SUM('Picks'!$BX$2:$BX$36),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$33)</f>
+        <f>SUM('Picks'!$BY$2:$BY$36)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$33,"&lt;&gt;",'Picks'!$AB$2:$AB$33),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$36,"&lt;&gt;",'Picks'!$AB$2:$AB$36),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$33,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$33,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$33,'Picks'!$AM$2:$AM$33,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$36,'Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A14,'Picks'!$U$2:$U$33,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A15,'Picks'!$U$2:$U$33,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled",'Picks'!$V$2:$V$33,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$33,'Picks'!$H$2:$H$33,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$33,'Picks'!$H$2:$H$33,$A16,'Picks'!$U$2:$U$33,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS33"/>
+  <dimension ref="A1:CS36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7759,18 +7759,38 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>0.9058</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:55.373994Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
@@ -7913,8 +7933,12 @@
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -8614,18 +8638,38 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:22.772699Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-berg-xi-2026-08-05).</t>
@@ -8768,8 +8812,12 @@
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8883,18 +8931,38 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>1.0294</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:24.139997Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-falf-sag-2026-08-05).</t>
@@ -9037,8 +9105,12 @@
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -9074,12 +9146,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>590bc13276b8452a</t>
+          <t>700dc7eb172049f7</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-05T17:05:00.161606Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9124,20 +9196,20 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.08</v>
+        <v>1.75188</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.570815</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.748624</v>
+        <v>0.74863</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.267855</v>
+        <v>0.177815</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>100</v>
@@ -9166,7 +9238,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-pure-drama-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-pure-drama-2026-08-05).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9250,7 +9322,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9265,7 +9337,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>19e41252784d7f0fb30ba60bf91a0e18dad6024caa2bc77a8c0649a56dcc9142</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9285,7 +9357,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:19.555277Z</t>
+          <t>2026-08-05T17:04:43.266243Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9295,13 +9367,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.08</v>
+        <v>1.75188</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.570815</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9343,12 +9415,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>ca5840fb1db34889</t>
+          <t>fc9a348be3044e45</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-06T00:24:54.248921Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9358,7 +9430,7 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>70562</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9368,12 +9440,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>WRAITH PCIFIC</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9393,49 +9465,63 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.460829</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.530945</v>
+        <v>0.605841</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.110777</v>
+        <v>0.145012</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="S29" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T29" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U29" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:58.366762Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-lav-bpl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-pcific-ttbs-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9445,7 +9531,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -9476,32 +9562,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>WRAITH PCIFIC</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>WRAITH PCIFIC</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>WRAITH PCIFIC</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9519,7 +9605,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9534,7 +9620,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9554,7 +9640,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:22.532084Z</t>
+          <t>2026-08-06T00:24:37.231379Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9564,13 +9650,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.460829</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9612,12 +9698,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>502da86df76d4f01</t>
+          <t>0c1c2c0e06274713</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-06T00:24:54.248921Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9627,7 +9713,7 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>70562</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9637,12 +9723,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9662,26 +9748,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.420168</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.606164</v>
+        <v>0.5310550000000001</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.155714</v>
+        <v>0.110887</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9690,21 +9776,35 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:00.154478Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-pcific-ttbs-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-lav-bpl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9714,7 +9814,7 @@
       </c>
       <c r="AG30" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH30" s="24" t="n"/>
@@ -9745,32 +9845,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>WRAITH PCIFIC</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9788,7 +9888,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9803,7 +9903,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9823,7 +9923,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:23.683454Z</t>
+          <t>2026-08-06T00:24:37.738828Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9833,13 +9933,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.420168</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9881,22 +9981,22 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>db86a6b057344de5</t>
+          <t>3b760535fa614d51</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-06T00:24:54.248921Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T10:30:00Z</t>
+          <t>2026-08-06T17:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>72651</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9906,12 +10006,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Yawara Esports</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Isurus</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9940,17 +10040,17 @@
         <v>0.570815</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.607715</v>
+        <v>0.745356</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.0369</v>
+        <v>0.174541</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -9959,21 +10059,35 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:51.262807Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-era-efa-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-isg-yaw-2026-08-06).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9983,7 +10097,7 @@
       </c>
       <c r="AG31" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH31" s="24" t="n"/>
@@ -10014,32 +10128,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Yawara Esports</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Yawara Esports</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Yawara Esports</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Isurus</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Isurus</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Isurus</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -10057,7 +10171,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -10072,7 +10186,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>95c0b03a7dffafd85c27ca9ed669e331e7385a1d064329e5a50c6fe806eb56d1</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -10092,7 +10206,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:26.353887Z</t>
+          <t>2026-08-06T00:24:47.216028Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -10150,22 +10264,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>990e0ba190de46ce</t>
+          <t>6e8f0b9c0ce949b1</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-06T03:30:48.016807Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T17:00:00Z</t>
+          <t>2026-08-06T08:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10175,12 +10289,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Yawara Esports</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Isurus</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10190,7 +10304,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -10200,26 +10314,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.724638</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.6</v>
+        <v>0.579832</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.746375</v>
+        <v>0.672341</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.146375</v>
+        <v>0.09250899999999999</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10228,21 +10342,35 @@
       </c>
       <c r="U32" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:02.991757Z</t>
+        </is>
+      </c>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-isg-yaw-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-efa-eac-2026-08-06).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10252,7 +10380,7 @@
       </c>
       <c r="AG32" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH32" s="24" t="n"/>
@@ -10283,32 +10411,32 @@
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>Yawara Esports</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Yawara Esports</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Yawara Esports</t>
+          <t>Esport Academy Copenhagen</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>Isurus</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Isurus</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Isurus</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10326,7 +10454,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>fe03335fd93db1544dba21d90e64b614b66d4504f6b07bd760b4633bb3785ef9</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10341,7 +10469,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>fe03335fd93db1544dba21d90e64b614b66d4504f6b07bd760b4633bb3785ef9</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10361,7 +10489,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:34.073375Z</t>
+          <t>2026-08-06T03:30:28.428004Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10371,13 +10499,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.724638</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.6</v>
+        <v>0.579832</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10419,12 +10547,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>d89c179c211c48b3</t>
+          <t>e001d63af3fa4b19</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:36.539226Z</t>
+          <t>2026-08-06T19:00:44.109783Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10469,23 +10597,23 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.409836</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.543196</v>
+        <v>0.542916</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.092746</v>
+        <v>0.13308</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="S33" s="29" t="n">
         <v>1</v>
@@ -10497,21 +10625,41 @@
       </c>
       <c r="U33" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V33" s="24" t="n"/>
-      <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y33" s="25" t="n"/>
-      <c r="Z33" s="26" t="n"/>
-      <c r="AA33" s="28" t="n"/>
-      <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
-      <c r="AD33" s="24" t="n"/>
+      <c r="Z33" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC33" s="30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:52.708995Z</t>
+        </is>
+      </c>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-mw-pcy-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-mw-pcy-2026-08-06).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10595,7 +10743,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>ba62d4174c52c7a2934bcbd8b028649e6d31b496f5b9eab70ce8b6a17fb58aa6</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10610,7 +10758,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>95ef3685860928d3c12125a00cdf074ac4e628138aac112a58082f0ead77ffde</t>
+          <t>ba62d4174c52c7a2934bcbd8b028649e6d31b496f5b9eab70ce8b6a17fb58aa6</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10630,7 +10778,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:35.923759Z</t>
+          <t>2026-08-06T19:00:13.521189Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10640,19 +10788,23 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.409836</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
       <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
-      <c r="BR33" s="28" t="n"/>
+      <c r="BQ33" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR33" s="28" t="n">
+        <v>0.41</v>
+      </c>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
       <c r="BU33" s="25" t="n"/>
@@ -10685,6 +10837,813 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>66d551cf890f4729</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:16.691798Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>74184</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.651856</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.16166</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-pure-enr-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:04.782971Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>048ce170928043f6</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:16.691798Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>74187</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.584786</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.184786</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-enr-for-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>ENRAGE</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:06.305684Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>9c28594db33c465c</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:16.691798Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>72721</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>SINQU Rehti</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.584222</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.123393</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-psna-sri-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>SINQU Rehti</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>SINQU Rehti</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>SINQU Rehti</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:08.265612Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS36" headerRowCount="1">
-  <autoFilter ref="A1:CS36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS35" headerRowCount="1">
+  <autoFilter ref="A1:CS35"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$36)</f>
+        <f>COUNTA('Picks'!$A$2:$A$35)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$36,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$36,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$36,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$35,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")/(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")/(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$36)/SUM('Picks'!$BX$2:$BX$36),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$35)/SUM('Picks'!$BX$2:$BX$35),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$36)</f>
+        <f>SUM('Picks'!$BY$2:$BY$35)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$36,"&lt;&gt;",'Picks'!$AB$2:$AB$36),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$35,"&lt;&gt;",'Picks'!$AB$2:$AB$35),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$36,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$36,'Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$35,'Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS36"/>
+  <dimension ref="A1:CS35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10918,18 +10918,38 @@
       </c>
       <c r="U34" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y34" s="25" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
+      <c r="Z34" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC34" s="30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:26.946203Z</t>
+        </is>
+      </c>
       <c r="AE34" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-pure-enr-2026-08-07).</t>
@@ -11072,8 +11092,12 @@
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
       <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
-      <c r="BR34" s="28" t="n"/>
+      <c r="BQ34" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR34" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
       <c r="BU34" s="25" t="n"/>
@@ -11109,22 +11133,22 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>048ce170928043f6</t>
+          <t>9b69d2b938034063</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:16.691798Z</t>
+          <t>2026-08-07T18:31:27.564017Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T18:30:00Z</t>
+          <t>2026-08-08T08:00:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>74187</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -11134,12 +11158,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>SINQU Rehti</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>ENRAGE</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -11149,7 +11173,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -11168,11 +11192,11 @@
         <v>0.4</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.584786</v>
+        <v>0.583902</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.184786</v>
+        <v>0.183902</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>100</v>
@@ -11201,7 +11225,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-enr-for-2026-08-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-psna-sri-2026-08-08).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -11242,32 +11266,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>SINQU Rehti</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>SINQU Rehti</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>SINQU Rehti</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>ENRAGE</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>ENRAGE</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>ENRAGE</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -11285,7 +11309,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+          <t>f2e7f884fc01634e12d74f8812661c5cb67e5be22fb9ba0e801020448143127e</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -11300,7 +11324,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
+          <t>f2e7f884fc01634e12d74f8812661c5cb67e5be22fb9ba0e801020448143127e</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -11320,7 +11344,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:06.305684Z</t>
+          <t>2026-08-07T18:31:09.334825Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -11375,275 +11399,6 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>9c28594db33c465c</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T15:24:16.691798Z</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>72721</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>SINQU Rehti</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N36" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0.584222</v>
-      </c>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n">
-        <v>0.123393</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>82</v>
-      </c>
-      <c r="S36" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U36" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-psna-sri-2026-08-08).</t>
-        </is>
-      </c>
-      <c r="AF36" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH36" s="24" t="n"/>
-      <c r="AI36" s="31" t="n"/>
-      <c r="AJ36" s="31" t="n"/>
-      <c r="AK36" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL36" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN36" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP36" s="24" t="inlineStr">
-        <is>
-          <t>SINQU Rehti</t>
-        </is>
-      </c>
-      <c r="AQ36" s="24" t="inlineStr">
-        <is>
-          <t>SINQU Rehti</t>
-        </is>
-      </c>
-      <c r="AR36" s="24" t="inlineStr">
-        <is>
-          <t>SINQU Rehti</t>
-        </is>
-      </c>
-      <c r="AS36" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AT36" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AU36" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AV36" s="24" t="n"/>
-      <c r="AW36" s="24" t="n"/>
-      <c r="AX36" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY36" s="24" t="n"/>
-      <c r="AZ36" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA36" s="24" t="inlineStr">
-        <is>
-          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
-        </is>
-      </c>
-      <c r="BB36" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD36" s="24" t="inlineStr">
-        <is>
-          <t>b8dea04ff55d1b5077c8587b9b9ed16ddeb7be47d75c96d6954498aa5ae37cd0</t>
-        </is>
-      </c>
-      <c r="BE36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH36" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T15:24:08.265612Z</t>
-        </is>
-      </c>
-      <c r="BI36" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ36" s="25" t="n"/>
-      <c r="BK36" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL36" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM36" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN36" s="28" t="n"/>
-      <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
-      <c r="BS36" s="28" t="n"/>
-      <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
-      <c r="BV36" s="29" t="n"/>
-      <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
-      <c r="BZ36" s="24" t="n"/>
-      <c r="CA36" s="31" t="n"/>
-      <c r="CB36" s="24" t="n"/>
-      <c r="CC36" s="24" t="n"/>
-      <c r="CD36" s="24" t="n"/>
-      <c r="CE36" s="24" t="n"/>
-      <c r="CF36" s="24" t="n"/>
-      <c r="CG36" s="24" t="n"/>
-      <c r="CH36" s="24" t="n"/>
-      <c r="CI36" s="24" t="n"/>
-      <c r="CJ36" s="24" t="n"/>
-      <c r="CK36" s="24" t="n"/>
-      <c r="CL36" s="24" t="n"/>
-      <c r="CM36" s="24" t="n"/>
-      <c r="CN36" s="24" t="n"/>
-      <c r="CO36" s="24" t="n"/>
-      <c r="CP36" s="24" t="n"/>
-      <c r="CQ36" s="24" t="n"/>
-      <c r="CR36" s="24" t="n"/>
-      <c r="CS36" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/cs2.xlsx
+++ b/data/gated_research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS76" headerRowCount="1">
-  <autoFilter ref="A1:CS76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS77" headerRowCount="1">
+  <autoFilter ref="A1:CS77"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$76)</f>
+        <f>COUNTA('Picks'!$A$2:$A$77)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$76,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$77,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$76,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")+COUNTIFS('Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$76,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$77,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")/(COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")+COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")/(COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"win")+COUNTIFS('Picks'!$BX$2:$BX$77,"&gt;0",'Picks'!$V$2:$V$77,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$76)/SUM('Picks'!$BX$2:$BX$76),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$77)/SUM('Picks'!$BX$2:$BX$77),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$76)</f>
+        <f>SUM('Picks'!$BY$2:$BY$77)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$76,"&lt;&gt;",'Picks'!$AB$2:$AB$76),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$77,"&lt;&gt;",'Picks'!$AB$2:$AB$77),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$76,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$76,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$76,'Picks'!$AM$2:$AM$76,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$77,'Picks'!$AM$2:$AM$77,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A14,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A15,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled",'Picks'!$V$2:$V$77,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$77,'Picks'!$H$2:$H$77,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$77,'Picks'!$H$2:$H$77,$A16,'Picks'!$U$2:$U$77,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS76"/>
+  <dimension ref="A1:CS77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23180,6 +23180,275 @@
         </is>
       </c>
     </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>84c8dfa6563745f2</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:22.932119Z</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>79707</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J77" s="25" t="n"/>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M77" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N77" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>0.589871</v>
+      </c>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="28" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S77" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U77" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="25" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="28" t="n"/>
+      <c r="AB77" s="28" t="n"/>
+      <c r="AC77" s="30" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-exmana-sawy-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF77" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG77" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="31" t="n"/>
+      <c r="AJ77" s="31" t="n"/>
+      <c r="AK77" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL77" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN77" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO77" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP77" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AQ77" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AR77" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AS77" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AT77" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AU77" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA77" s="24" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="BB77" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD77" s="24" t="inlineStr">
+        <is>
+          <t>707a22aae8ecc986a21e2f01b4e3f94c78e29cfde24e72fe5d7d72a0990bd6c9</t>
+        </is>
+      </c>
+      <c r="BE77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG77" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:12.073189Z</t>
+        </is>
+      </c>
+      <c r="BI77" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ77" s="25" t="n"/>
+      <c r="BK77" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL77" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM77" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN77" s="28" t="n"/>
+      <c r="BO77" s="28" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
+      <c r="BT77" s="28" t="n"/>
+      <c r="BU77" s="25" t="n"/>
+      <c r="BV77" s="29" t="n"/>
+      <c r="BW77" s="24" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
+      <c r="BZ77" s="24" t="n"/>
+      <c r="CA77" s="31" t="n"/>
+      <c r="CB77" s="24" t="n"/>
+      <c r="CC77" s="24" t="n"/>
+      <c r="CD77" s="24" t="n"/>
+      <c r="CE77" s="24" t="n"/>
+      <c r="CF77" s="24" t="n"/>
+      <c r="CG77" s="24" t="n"/>
+      <c r="CH77" s="24" t="n"/>
+      <c r="CI77" s="24" t="n"/>
+      <c r="CJ77" s="24" t="n"/>
+      <c r="CK77" s="24" t="n"/>
+      <c r="CL77" s="24" t="n"/>
+      <c r="CM77" s="24" t="n"/>
+      <c r="CN77" s="24" t="n"/>
+      <c r="CO77" s="24" t="n"/>
+      <c r="CP77" s="24" t="n"/>
+      <c r="CQ77" s="24" t="n"/>
+      <c r="CR77" s="24" t="n"/>
+      <c r="CS77" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
